--- a/data/daily/2026-08/2026-08-31.xlsx
+++ b/data/daily/2026-08/2026-08-31.xlsx
@@ -1195,14 +1195,39 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,92 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1450,27 +1450,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,49 +1503,124 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,129 +1628,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -3011,7 +3011,7 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3019,34 +3019,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32,800원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11839566</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3054,27 +3054,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>32,800원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/11839566</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
           <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
           <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
           <t>32,800원</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4077,19 +4077,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/wJCESiflDyulw8oZ8pW1601618642_00_00wJCESiflDyulw8oZ8pW1.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4112,19 +4112,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762105&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/6YtHsleJV0YMOtFdtOAk901762105_00_016YtHsleJV0YMOtFdtOAk.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
     </row>
@@ -4167,34 +4167,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/RhgSqjNOPs6aCmkpEpj2030086178_00_00RhgSqjNOPs6aCmkpEpj2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 관절 건강 올인원 15포 15일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4217,19 +4217,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991020&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/yH5aOMk0fGfjGGk0S84s033991020_00_00yH5aOMk0fGfjGGk0S84s.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/jrLxfLkWCczsCAsnqLoJ613602131_00_01jrLxfLkWCczsCAsnqLoJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,27 +4272,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 풍성한 판토텐산 비오틴 올인원 15포 15일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991019&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/JA7ke0629R2muBbsNQbJ033991019_00_00JA7ke0629R2muBbsNQbJ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
     </row>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4322,19 +4322,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000139&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/Am2C7Da2wracg1TigkAF600000139_00_00Am2C7Da2wracg1TigkAF.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,34 +4342,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오브맘 활력에너지B 하루구미 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/FWBWePRv27KbgtvBHof6613602132_00_01FWBWePRv27KbgtvBHof6.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
     </row>
@@ -4517,47 +4517,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
         </is>
       </c>
     </row>
@@ -4569,47 +4569,47 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 관절 건강 올인원 15포 15일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 풍성한 판토텐산 비오틴 올인원 15포 15일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 활력에너지B 하루구미 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -4698,32 +4698,32 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
           <t>1,000원</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -4875,34 +4875,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[8/31하루특가/9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>[8/31 하루특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>14,500원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807370ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355473ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,27 +4910,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[8/31 하루특가/스테디셀러특가] [감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14,500원</t>
+          <t>12,940원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236701&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355473ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023670137ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -4945,27 +4945,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>[8/31하루특가/9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24,460원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733450ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807370ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>덴프스 트루바이타민 액티브 10+4포 증정기획 (2주분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5025,24 +5025,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>31,300원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263560&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026356006ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265832ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,34 +5050,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[올영단독] 세노비스 트리플러스 오메가3 이뮨 우먼/맨 80+10캡슐 기획(45일분)</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>세노비스</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26,000원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000232269&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023226907ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,27 +5085,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CJ 한뿌리 흑삼지천보 진녹 30포 (1개월분) (온)</t>
+          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>한뿌리</t>
+          <t>비비랩</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>112,500원</t>
+          <t>22,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247763&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000208888&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024776301ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020888841ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[웰니스 특가]올더베러 웰니스 구미 30일분 택1</t>
+          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8,800원</t>
+          <t>26,370원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587417ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846229ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,27 +5155,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26,370원</t>
+          <t>9,600원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846229ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>그레인온 파로효소 골드 캡슐레이션 30포 (1개월분)</t>
+          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>락토핏</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18,910원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259818&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025981802ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5330,42 +5330,42 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5382,19 +5382,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>닥터아돌</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>프로뉴트리션</t>
@@ -5407,27 +5407,27 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>세노비스</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>한뿌리</t>
+          <t>비비랩</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>락토핏</t>
         </is>
       </c>
     </row>
@@ -5439,19 +5439,19 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[8/31 하루특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[8/31하루특가/9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[8/31 하루특가/스테디셀러특가] [감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>[8/31 하루특가/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
@@ -5459,32 +5459,32 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 트루바이타민 액티브 10+4포 증정기획 (2주분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[올영단독] 세노비스 트리플러스 오메가3 이뮨 우먼/맨 80+10캡슐 기획(45일분)</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>CJ 한뿌리 흑삼지천보 진녹 30포 (1개월분) (온)</t>
+          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[웰니스 특가]올더베러 웰니스 구미 30일분 택1</t>
+          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>그레인온 파로효소 골드 캡슐레이션 30포 (1개월분)</t>
+          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
     </row>
@@ -5496,19 +5496,19 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>14,500원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>12,940원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>21,900원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>14,500원</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>24,460원</t>
-        </is>
-      </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
           <t>32,500원</t>
@@ -5516,32 +5516,32 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>31,300원</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>26,000원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>112,500원</t>
+          <t>22,900원</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>8,800원</t>
+          <t>26,370원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26,370원</t>
+          <t>9,600원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>18,910원</t>
+          <t>17,900원</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>42.5</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -5683,70 +5683,70 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -5755,17 +5755,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -5781,16 +5781,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -5799,7 +5799,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5812,16 +5812,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5838,6 +5838,72 @@
       </c>
       <c r="F9" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
